--- a/artfynd/A 57827-2024 artfynd.xlsx
+++ b/artfynd/A 57827-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89604142</v>
+        <v>89604164</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442360.7742756327</v>
+        <v>442381</v>
       </c>
       <c r="R2" t="n">
-        <v>6941535.119186094</v>
+        <v>6941541</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89604182</v>
+        <v>89604179</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442402.9708191279</v>
+        <v>442370</v>
       </c>
       <c r="R3" t="n">
-        <v>6941521.026045416</v>
+        <v>6941472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89604164</v>
+        <v>89604191</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442381.1784055176</v>
+        <v>442415</v>
       </c>
       <c r="R4" t="n">
-        <v>6941541.213545199</v>
+        <v>6941540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89604191</v>
+        <v>89604142</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442414.8366094214</v>
+        <v>442361</v>
       </c>
       <c r="R5" t="n">
-        <v>6941540.167674609</v>
+        <v>6941535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1079,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89604179</v>
+        <v>131293320</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>223284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442369.8227897601</v>
+        <v>442392</v>
       </c>
       <c r="R6" t="n">
-        <v>6941471.850229057</v>
+        <v>6941471</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,24 +1149,24 @@
           <t>Vemdalen</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>af4f3184-bb2e-41bf-baa6-894e920a55d8</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal hamlad sälg med spår av yxhugg ovan beteshöjd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,69 +1181,71 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Via Bodil Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>235563</v>
+        <v>131293482</v>
       </c>
       <c r="B7" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>223284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>443178.757123064</v>
+        <v>442372</v>
       </c>
       <c r="R7" t="n">
-        <v>6941485.057171271</v>
+        <v>6941484</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,24 +1267,24 @@
           <t>Vemdalen</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>66004496-746c-4bdb-9437-d89490335701</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal sälg som tippat</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,50 +1295,30 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sini Saarela</t>
+          <t>Bodil Carlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sini Saarela, * Naturskyddare</t>
+          <t>Via Bodil Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>350109</v>
+        <v>235562</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>443225.4816810056</v>
+        <v>443580</v>
       </c>
       <c r="R8" t="n">
-        <v>6941411.930759055</v>
+        <v>6941427</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,21 +1383,11 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1491,6 +1405,11 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1512,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>235562</v>
+        <v>235563</v>
       </c>
       <c r="B9" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,12 +1451,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1552,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443580.0430210665</v>
+        <v>443179</v>
       </c>
       <c r="R9" t="n">
-        <v>6941427.064900293</v>
+        <v>6941485</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1585,19 +1499,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>350110</v>
+        <v>89604187</v>
       </c>
       <c r="B10" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,21 +1558,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443178.5012960753</v>
+        <v>442696</v>
       </c>
       <c r="R10" t="n">
-        <v>6941497.038862245</v>
+        <v>6940918</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,22 +1612,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,67 +1628,52 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sini Saarela</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sini Saarela, * Naturskyddare</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>483350</v>
+        <v>89604189</v>
       </c>
       <c r="B11" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1809,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443045.4796800767</v>
+        <v>442785</v>
       </c>
       <c r="R11" t="n">
-        <v>6941514.524889305</v>
+        <v>6940917</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,22 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,50 +1729,30 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sini Saarela</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sini Saarela, * Naturskyddare</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>350108</v>
+        <v>89604150</v>
       </c>
       <c r="B12" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,13 +1784,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443505.5527562177</v>
+        <v>442733</v>
       </c>
       <c r="R12" t="n">
-        <v>6941387.334152488</v>
+        <v>6941378</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1970,22 +1814,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,45 +1830,30 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sini Saarela</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sini Saarela, * Naturskyddare</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>350107</v>
+        <v>89604177</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2066,13 +1885,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443632.0484817358</v>
+        <v>442770</v>
       </c>
       <c r="R13" t="n">
-        <v>6941419.730278683</v>
+        <v>6940930</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,22 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,67 +1931,52 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sini Saarela</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sini Saarela, * Naturskyddare</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89604193</v>
+        <v>350107</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2192,13 +1986,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442777.108000293</v>
+        <v>443632</v>
       </c>
       <c r="R14" t="n">
-        <v>6940987.040130871</v>
+        <v>6941420</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2222,22 +2016,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,57 +2032,62 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sini Saarela</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sini Saarela, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89604175</v>
+        <v>350108</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2308,13 +2097,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442713.8980407004</v>
+        <v>443506</v>
       </c>
       <c r="R15" t="n">
-        <v>6940907.041461666</v>
+        <v>6941387</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2338,22 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,57 +2143,62 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sini Saarela</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sini Saarela, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89604171</v>
+        <v>350109</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442753.8536334437</v>
+        <v>443225</v>
       </c>
       <c r="R16" t="n">
-        <v>6940922.937897074</v>
+        <v>6941412</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2454,22 +2238,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2480,57 +2254,62 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sini Saarela</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sini Saarela, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89604162</v>
+        <v>350110</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2540,13 +2319,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442708.9465988802</v>
+        <v>443179</v>
       </c>
       <c r="R17" t="n">
-        <v>6941367.844106565</v>
+        <v>6941497</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2570,22 +2349,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2596,57 +2365,62 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sini Saarela</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sini Saarela, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89604154</v>
+        <v>89604145</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442689.0430938693</v>
+        <v>442800</v>
       </c>
       <c r="R18" t="n">
-        <v>6941364.042164155</v>
+        <v>6940910</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2689,19 +2463,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2732,37 +2496,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89604176</v>
+        <v>89604190</v>
       </c>
       <c r="B19" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2772,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443023.881322553</v>
+        <v>442897</v>
       </c>
       <c r="R19" t="n">
-        <v>6941090.137804048</v>
+        <v>6941324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,19 +2564,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,15 +2597,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89604146</v>
+        <v>89604139</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,21 +2608,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2888,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442954.9102161271</v>
+        <v>442716</v>
       </c>
       <c r="R20" t="n">
-        <v>6941237.830875349</v>
+        <v>6940837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,24 +2665,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2969,15 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89604170</v>
+        <v>89604141</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3009,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443019.8531365789</v>
+        <v>442761</v>
       </c>
       <c r="R21" t="n">
-        <v>6941151.021806371</v>
+        <v>6940935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,19 +2766,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3085,15 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89604163</v>
+        <v>89604154</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3101,21 +2810,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3125,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442711.9500308066</v>
+        <v>442689</v>
       </c>
       <c r="R22" t="n">
-        <v>6940927.8087761</v>
+        <v>6941364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3158,19 +2867,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,15 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89604190</v>
+        <v>89604155</v>
       </c>
       <c r="B23" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3217,21 +2911,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3241,10 +2935,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442896.8809428213</v>
+        <v>442715</v>
       </c>
       <c r="R23" t="n">
-        <v>6941324.059230304</v>
+        <v>6941361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3274,19 +2968,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3317,15 +3001,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89604168</v>
+        <v>89604158</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,21 +3012,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3357,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442717.8021043466</v>
+        <v>442606</v>
       </c>
       <c r="R24" t="n">
-        <v>6940865.967065659</v>
+        <v>6941317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3390,19 +3069,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3433,15 +3102,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89604159</v>
+        <v>89604161</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3449,21 +3113,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3473,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442937.9546460102</v>
+        <v>442823</v>
       </c>
       <c r="R25" t="n">
-        <v>6940922.987835338</v>
+        <v>6941354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3506,19 +3170,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3549,15 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89604169</v>
+        <v>89604174</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,21 +3214,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3589,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442798.1896867562</v>
+        <v>442625</v>
       </c>
       <c r="R26" t="n">
-        <v>6941433.100770202</v>
+        <v>6941325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3622,19 +3271,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,15 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89604195</v>
+        <v>89604175</v>
       </c>
       <c r="B27" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,10 +3339,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442802.1973895301</v>
+        <v>442714</v>
       </c>
       <c r="R27" t="n">
-        <v>6941398.020049267</v>
+        <v>6940907</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3738,19 +3372,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3781,15 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89604184</v>
+        <v>89604176</v>
       </c>
       <c r="B28" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3797,21 +3416,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3821,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442828.2053562395</v>
+        <v>443024</v>
       </c>
       <c r="R28" t="n">
-        <v>6940899.999137687</v>
+        <v>6941090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3854,19 +3473,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3897,15 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89604186</v>
+        <v>89604195</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3913,21 +3517,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3937,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442807.8829499205</v>
+        <v>442802</v>
       </c>
       <c r="R29" t="n">
-        <v>6941379.955314456</v>
+        <v>6941398</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3970,19 +3574,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4013,37 +3607,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89604178</v>
+        <v>483350</v>
       </c>
       <c r="B30" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4053,13 +3642,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442701.1650232415</v>
+        <v>443045</v>
       </c>
       <c r="R30" t="n">
-        <v>6940891.135351309</v>
+        <v>6941515</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4083,22 +3672,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4109,57 +3688,67 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sini Saarela</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Sini Saarela, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89604157</v>
+        <v>89604147</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4169,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442815.082167574</v>
+        <v>442771</v>
       </c>
       <c r="R31" t="n">
-        <v>6940995.138583428</v>
+        <v>6941404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4202,19 +3791,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4245,37 +3824,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89604149</v>
+        <v>89604151</v>
       </c>
       <c r="B32" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4285,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442688.9504571033</v>
+        <v>442852</v>
       </c>
       <c r="R32" t="n">
-        <v>6940931.892438856</v>
+        <v>6940922</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4318,19 +3892,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4361,19 +3925,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89604188</v>
+        <v>89604153</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4401,10 +3960,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442845.0263042951</v>
+        <v>442686</v>
       </c>
       <c r="R33" t="n">
-        <v>6941340.156085395</v>
+        <v>6940938</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4434,19 +3993,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4477,37 +4026,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89604150</v>
+        <v>89604157</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4517,10 +4061,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442733.1123390831</v>
+        <v>442815</v>
       </c>
       <c r="R34" t="n">
-        <v>6941378.022065404</v>
+        <v>6940995</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4550,19 +4094,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4593,37 +4127,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89604187</v>
+        <v>89604160</v>
       </c>
       <c r="B35" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4633,10 +4162,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>442696.0917506854</v>
+        <v>442932</v>
       </c>
       <c r="R35" t="n">
-        <v>6940917.946541178</v>
+        <v>6940916</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4666,19 +4195,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4709,15 +4228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89604147</v>
+        <v>89604170</v>
       </c>
       <c r="B36" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,21 +4239,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4749,10 +4263,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>442770.9312138111</v>
+        <v>443020</v>
       </c>
       <c r="R36" t="n">
-        <v>6941404.088132909</v>
+        <v>6941151</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4782,19 +4296,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4825,37 +4329,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89604165</v>
+        <v>89604171</v>
       </c>
       <c r="B37" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4865,10 +4364,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442687.1982723825</v>
+        <v>442754</v>
       </c>
       <c r="R37" t="n">
-        <v>6941364.074075958</v>
+        <v>6940923</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4898,19 +4397,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4941,37 +4430,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89604177</v>
+        <v>89604180</v>
       </c>
       <c r="B38" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4981,10 +4465,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442770.1252480933</v>
+        <v>442941</v>
       </c>
       <c r="R38" t="n">
-        <v>6940930.028775678</v>
+        <v>6940959</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5014,19 +4498,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5057,37 +4531,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89604189</v>
+        <v>89604188</v>
       </c>
       <c r="B39" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5097,10 +4566,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442785.124339705</v>
+        <v>442845</v>
       </c>
       <c r="R39" t="n">
-        <v>6940916.868872532</v>
+        <v>6941340</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5130,19 +4599,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5173,37 +4632,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89604148</v>
+        <v>89604193</v>
       </c>
       <c r="B40" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5213,10 +4667,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442799.7735914299</v>
+        <v>442777</v>
       </c>
       <c r="R40" t="n">
-        <v>6940910.165507364</v>
+        <v>6940987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,19 +4700,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,15 +4733,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89604192</v>
+        <v>89604165</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5305,21 +4744,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5329,10 +4768,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442916.8474659543</v>
+        <v>442687</v>
       </c>
       <c r="R41" t="n">
-        <v>6940929.801794468</v>
+        <v>6941364</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5362,24 +4801,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5410,15 +4834,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89604151</v>
+        <v>89604146</v>
       </c>
       <c r="B42" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5426,21 +4845,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5450,10 +4869,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442852.1193533023</v>
+        <v>442955</v>
       </c>
       <c r="R42" t="n">
-        <v>6940922.163278464</v>
+        <v>6941238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5483,19 +4902,14 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5526,15 +4940,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89604194</v>
+        <v>89604181</v>
       </c>
       <c r="B43" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5566,10 +4975,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442937.786849044</v>
+        <v>442798</v>
       </c>
       <c r="R43" t="n">
-        <v>6940940.038265244</v>
+        <v>6940920</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5599,19 +5008,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5647,15 +5046,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>89604180</v>
+        <v>89604192</v>
       </c>
       <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5663,21 +5057,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5687,10 +5081,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>442940.8796135038</v>
+        <v>442917</v>
       </c>
       <c r="R44" t="n">
-        <v>6940958.875424988</v>
+        <v>6940930</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5720,19 +5114,14 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,15 +5152,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>89604145</v>
+        <v>89604194</v>
       </c>
       <c r="B45" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5779,21 +5163,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5803,10 +5187,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442799.7735914299</v>
+        <v>442938</v>
       </c>
       <c r="R45" t="n">
-        <v>6940910.165507364</v>
+        <v>6940940</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5836,19 +5220,14 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5879,37 +5258,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>89604139</v>
+        <v>89604172</v>
       </c>
       <c r="B46" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5919,10 +5293,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442715.9166525541</v>
+        <v>442796</v>
       </c>
       <c r="R46" t="n">
-        <v>6940836.971989991</v>
+        <v>6940986</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5952,19 +5326,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,32 +5359,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>89604181</v>
+        <v>89604144</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6035,10 +5394,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442798.0954887121</v>
+        <v>442641</v>
       </c>
       <c r="R47" t="n">
-        <v>6940919.870169068</v>
+        <v>6941320</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6068,24 +5427,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6116,15 +5460,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>89604141</v>
+        <v>89604143</v>
       </c>
       <c r="B48" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6132,21 +5471,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6156,10 +5495,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442760.9794952575</v>
+        <v>442810</v>
       </c>
       <c r="R48" t="n">
-        <v>6940934.794190947</v>
+        <v>6940934</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6189,19 +5528,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6232,15 +5561,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>89604160</v>
+        <v>89604156</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6248,21 +5572,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6272,10 +5596,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442931.8391941296</v>
+        <v>442872</v>
       </c>
       <c r="R49" t="n">
-        <v>6940916.181957201</v>
+        <v>6940910</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6305,19 +5629,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6348,15 +5662,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>89604167</v>
+        <v>89604148</v>
       </c>
       <c r="B50" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6364,21 +5673,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6388,10 +5697,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442825.9947111343</v>
+        <v>442800</v>
       </c>
       <c r="R50" t="n">
-        <v>6940878.842742437</v>
+        <v>6940910</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6421,19 +5730,9 @@
           <t>2020-10-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6464,19 +5763,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>89604153</v>
+        <v>92498199</v>
       </c>
       <c r="B51" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6500,17 +5794,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Landaråsen, Hjd</t>
+          <t>Per i Vallmyren (UE 27), Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442685.8251645277</v>
+        <v>443100</v>
       </c>
       <c r="R51" t="n">
-        <v>6940937.936180066</v>
+        <v>6939906</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6534,22 +5828,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6560,487 +5844,24 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>89604143</v>
-      </c>
-      <c r="B52" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Landaråsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>442809.8735982554</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6940933.949993482</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>89604161</v>
-      </c>
-      <c r="B53" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Landaråsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>442823.1187792649</v>
-      </c>
-      <c r="R53" t="n">
-        <v>6941353.894007912</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>89604155</v>
-      </c>
-      <c r="B54" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Landaråsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>442714.822818875</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6941360.832217595</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>89604173</v>
-      </c>
-      <c r="B55" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Landaråsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>442880.9370593312</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6941335.85129353</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57827-2024 artfynd.xlsx
+++ b/artfynd/A 57827-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604164</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604191</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604142</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293320</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293482</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604187</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604154</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604158</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604174</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604165</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604144</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235562</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235563</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604189</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,6 +2538,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604150</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2554,6 +2644,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604177</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/350107</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2776,6 +2876,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/350108</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2887,6 +2992,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/350109</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2998,6 +3108,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/350110</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3099,6 +3214,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604145</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3200,6 +3320,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604190</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3301,6 +3426,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604139</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3402,6 +3532,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604141</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3503,6 +3638,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604155</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3604,6 +3744,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604161</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3705,6 +3850,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604175</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3806,6 +3956,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604176</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3907,6 +4062,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604195</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4023,6 +4183,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/483350</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4124,6 +4289,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604147</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4225,6 +4395,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604151</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4326,6 +4501,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604157</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4427,6 +4607,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604160</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4528,6 +4713,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604170</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4629,6 +4819,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604171</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4730,6 +4925,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604180</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4831,6 +5031,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604188</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4932,6 +5137,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604193</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5038,6 +5248,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604146</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5144,6 +5359,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604181</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5250,6 +5470,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604192</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5356,6 +5581,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604194</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5457,6 +5687,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604172</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5558,6 +5793,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604143</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5659,6 +5899,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604156</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5760,6 +6005,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604148</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5862,8 +6112,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92498199</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>